--- a/tool/package-generator/config/package_definition.xlsx
+++ b/tool/package-generator/config/package_definition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7448288E-E729-4371-B32A-30E5E391C178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F217B6-FA65-45A0-9790-F22FDCC34F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テンプレート" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t>No</t>
     <phoneticPr fontId="2"/>
@@ -63,6 +63,13 @@
     <rPh sb="2" eb="3">
       <t>サキ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>.\a\新規 テキスト ドキュメント.txt</t>
+  </si>
+  <si>
+    <t>.\a\新規 テキスト ドキュメント.txt</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -412,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="3.8984375" bestFit="1" customWidth="1"/>
@@ -436,6 +443,14 @@
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -474,7 +489,9 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
@@ -485,6 +502,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101003F084FCF046B4A45A11E77E3180ECC70" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="93b3c00843758588d82b9b1cc445674f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a016a34-9640-43fb-86ea-5daabefdfe7e" xmlns:ns3="2d3c347e-deae-4f57-8eaf-3772dd4433c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3ba47e2a8c0ba124aa1c5a854c46141a" ns2:_="" ns3:_="">
     <xsd:import namespace="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
@@ -679,27 +716,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
+    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143D2EB-8BE1-46FD-AA36-F0A52D61EC19}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -716,23 +752,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
-    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/tool/package-generator/config/package_definition.xlsx
+++ b/tool/package-generator/config/package_definition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F217B6-FA65-45A0-9790-F22FDCC34F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5CFB04-DBFC-4BB3-BCC3-5331D707DE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="8">
   <si>
     <t>No</t>
     <phoneticPr fontId="2"/>
@@ -67,10 +67,13 @@
   </si>
   <si>
     <t>.\a\新規 テキスト ドキュメント.txt</t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>.\a\新規 テキスト ドキュメント.txt</t>
-    <phoneticPr fontId="2"/>
+    <t>.\config\package_definition.xlsx</t>
+  </si>
+  <si>
+    <t>.\config\README.md</t>
   </si>
 </sst>
 </file>
@@ -419,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="3.8984375" bestFit="1" customWidth="1"/>
@@ -450,7 +453,15 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -461,7 +472,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75150BA2-5956-4186-B987-ACE3C5F8C674}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="3.8984375" bestFit="1" customWidth="1"/>
@@ -490,10 +501,20 @@
     <row r="2" spans="1:5">
       <c r="A2" s="2"/>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -502,26 +523,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101003F084FCF046B4A45A11E77E3180ECC70" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="93b3c00843758588d82b9b1cc445674f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a016a34-9640-43fb-86ea-5daabefdfe7e" xmlns:ns3="2d3c347e-deae-4f57-8eaf-3772dd4433c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3ba47e2a8c0ba124aa1c5a854c46141a" ns2:_="" ns3:_="">
     <xsd:import namespace="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
@@ -716,26 +717,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
-    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143D2EB-8BE1-46FD-AA36-F0A52D61EC19}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -752,4 +754,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
+    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>